--- a/public/exports-from-60-with-coowners/29188378.xlsx
+++ b/public/exports-from-60-with-coowners/29188378.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009921</t>
+          <t xml:space="preserve">200009922</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009922</t>
+          <t xml:space="preserve">200009923</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535912</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M184" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188378.xlsx
+++ b/public/exports-from-60-with-coowners/29188378.xlsx
@@ -8239,7 +8239,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009922</t>
+          <t xml:space="preserve">200009921</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">310001718</t>
+          <t xml:space="preserve">310001719</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535911</t>
+          <t xml:space="preserve">311535915</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M185" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188378.xlsx
+++ b/public/exports-from-60-with-coowners/29188378.xlsx
@@ -8314,7 +8314,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200009923</t>
+          <t xml:space="preserve">200009922</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">310001719</t>
+          <t xml:space="preserve">310001718</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535912</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535915</t>
+          <t xml:space="preserve">311535911</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
